--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C26FB9C-D49E-42BD-8B6A-33B8F792C803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E0F535859F2B225D2E36BEA071D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{756C3597-40F0-4292-A14F-3E63B8848D69}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejournalsystemer">'Opdateret d. 09-09-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejournalsystemer">'Opdateret d. 14-09-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -720,7 +720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -776,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -804,7 +804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -824,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -838,7 +838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -855,7 +855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -872,7 +872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -889,7 +889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -903,7 +903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -945,7 +945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -990,7 +990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>93</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>95</v>
       </c>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E0F535859F2B225D2E36BEA071D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{756C3597-40F0-4292-A14F-3E63B8848D69}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E0F535859F2B22A1CE3394E671D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A58764B6-AC3A-41BF-B4F3-D2E21BEBB31C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E0F535859F2B22A1CE3394E671D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A58764B6-AC3A-41BF-B4F3-D2E21BEBB31C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9602C5-8368-4AEC-B7F1-771DC9A96652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -720,7 +720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -776,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -804,7 +804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -824,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -838,7 +838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -855,7 +855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -872,7 +872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -889,7 +889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -903,7 +903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -945,7 +945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -990,7 +990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>93</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>95</v>
       </c>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9602C5-8368-4AEC-B7F1-771DC9A96652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C11CA5D-9517-4BC1-91F7-8C2BA969B611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejournalsystemer">'Opdateret d. 14-09-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejournalsystemer">'Opdateret d. 17-09-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -720,7 +720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -776,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -804,7 +804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -824,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -838,7 +838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -855,7 +855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -872,7 +872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -889,7 +889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -903,7 +903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -945,7 +945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -990,7 +990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>93</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>95</v>
       </c>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C11CA5D-9517-4BC1-91F7-8C2BA969B611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAA8CBD-1036-4596-948A-C4B76FF081B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAA8CBD-1036-4596-948A-C4B76FF081B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E0F535859F2B2208DEB1A2CA71D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07742C5E-43D0-4088-9173-854DE7AABE64}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejournalsystemer">'Opdateret d. 17-09-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejournalsystemer">'Opdateret d. 18-09-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -720,7 +720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -776,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -804,7 +804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -824,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -838,7 +838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -855,7 +855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -872,7 +872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -889,7 +889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -903,7 +903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -945,7 +945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -990,7 +990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>93</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>95</v>
       </c>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E0F535859F2B2208DEB1A2CA71D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07742C5E-43D0-4088-9173-854DE7AABE64}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E0F535859F2B22BF46F2A54070D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5502B215-E31F-474B-95CC-4B2245B94FE5}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejournalsystemer">'Opdateret d. 18-09-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejournalsystemer">'Opdateret d. 21-09-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E0F535859F2B22BF46F2A54070D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5502B215-E31F-474B-95CC-4B2245B94FE5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD365D8-B40D-4DF6-8CCC-8AE7BE113BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -720,7 +720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -776,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -804,7 +804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -824,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -838,7 +838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -855,7 +855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -872,7 +872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -889,7 +889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -903,7 +903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -945,7 +945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -990,7 +990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>93</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>95</v>
       </c>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD365D8-B40D-4DF6-8CCC-8AE7BE113BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1B5FA9-785B-40C8-A7DA-28FC402E54DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejournalsystemer">'Opdateret d. 21-09-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejournalsystemer">'Opdateret d. 22-09-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1B5FA9-785B-40C8-A7DA-28FC402E54DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF91846-85B4-4EAC-8028-B96E72AA5E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF91846-85B4-4EAC-8028-B96E72AA5E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C37C633-364A-44C6-B2BF-C06FA53C180B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejournalsystemer">'Opdateret d. 22-09-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejournalsystemer">'Opdateret d. 23-09-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C37C633-364A-44C6-B2BF-C06FA53C180B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E0F535859F2B22E206B096AE71D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FE40987-2AB8-443E-B259-DB6EA343C33D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -720,7 +720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -776,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -804,7 +804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -824,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -838,7 +838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -855,7 +855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -872,7 +872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -889,7 +889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -903,7 +903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -945,7 +945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -990,7 +990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>93</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>95</v>
       </c>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9E0F535859F2B22E206B096AE71D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FE40987-2AB8-443E-B259-DB6EA343C33D}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB90275F594692B22C9A630A1DE70D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F60DC883-EA8D-4F58-8E25-D1C521102721}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejournalsystemer">'Opdateret d. 23-09-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejournalsystemer">'Opdateret d. 24-09-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -61,7 +61,7 @@
     <t>APD-DK (2.0.1)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB90275F594692B22C9A630A1DE70D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F60DC883-EA8D-4F58-8E25-D1C521102721}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB90275F594692B229F8E35827671D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D885CE53-A87D-40E5-B992-1CB8BAE985FF}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB90275F594692B229F8E35827671D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D885CE53-A87D-40E5-B992-1CB8BAE985FF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458872B0-574E-463F-BC6B-8424151D8C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejournalsystemer">'Opdateret d. 24-09-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejournalsystemer">'Opdateret d. 28-09-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -720,7 +720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -776,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -804,7 +804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -824,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -838,7 +838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -855,7 +855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -872,7 +872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -889,7 +889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -903,7 +903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -945,7 +945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -990,7 +990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>93</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>95</v>
       </c>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{458872B0-574E-463F-BC6B-8424151D8C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB90275F594692B222F5670B71671D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B7EA480-DDAB-45E9-A045-9A7E22076EFD}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejournalsystemer">'Opdateret d. 28-09-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejournalsystemer">'Opdateret d. 02-10-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -720,7 +720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -776,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -804,7 +804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -824,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -838,7 +838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -855,7 +855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -872,7 +872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -889,7 +889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -903,7 +903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -945,7 +945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -990,7 +990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>93</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>95</v>
       </c>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AF91846-85B4-4EAC-8028-B96E72AA5E56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FCCDCD-8D21-4D27-B3A3-A5F0ED4A05B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejournalsystemer">'Opdateret d. 22-09-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejournalsystemer">'Opdateret d. 07-10-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -61,7 +61,7 @@
     <t>APD-DK (2.0.1)</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB90275F594692B222F5670B71671D86088" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B7EA480-DDAB-45E9-A045-9A7E22076EFD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530595E5-E141-435D-936D-7D07355BC695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejournalsystemer">'Opdateret d. 02-10-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejournalsystemer">'Opdateret d. 07-10-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -656,9 +656,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -692,7 +692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -706,7 +706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -720,7 +720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -734,7 +734,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -762,7 +762,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -776,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -790,7 +790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -804,7 +804,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -824,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>30</v>
       </c>
@@ -838,7 +838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -855,7 +855,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -872,7 +872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>36</v>
       </c>
@@ -889,7 +889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -903,7 +903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -917,7 +917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -931,7 +931,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
@@ -945,7 +945,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -962,7 +962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>47</v>
       </c>
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -990,7 +990,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1004,7 +1004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>20</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>52</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>54</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -1130,7 +1130,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>56</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>58</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>60</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>60</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>65</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>28</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -1265,7 +1265,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>36</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>70</v>
       </c>
@@ -1344,7 +1344,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>72</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>74</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>74</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>77</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>77</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>77</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>81</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -1456,7 +1456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>86</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>88</v>
       </c>
@@ -1521,7 +1521,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>90</v>
       </c>
@@ -1535,7 +1535,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>90</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>93</v>
       </c>
@@ -1563,7 +1563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>95</v>
       </c>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530595E5-E141-435D-936D-7D07355BC695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB90275F594692B2247FEB383EE70D86094" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF6CBBF3-0C2F-4D3C-AD00-63E481E0D6C3}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejournalsystemer">'Opdateret d. 07-10-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejournalsystemer">'Opdateret d. 08-10-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB90275F594692B2247FEB383EE70D86094" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF6CBBF3-0C2F-4D3C-AD00-63E481E0D6C3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25616B9A-BD71-4C6E-8610-08667D2A9E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejournalsystemer">'Opdateret d. 08-10-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejournalsystemer">'Opdateret d. 09-10-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25616B9A-BD71-4C6E-8610-08667D2A9E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2401FCA6-CDBC-4AC6-94A0-03E82849A07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Børnejournalsystemer_excel.XLSX
+++ b/html/Børnejournalsystemer_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2401FCA6-CDBC-4AC6-94A0-03E82849A07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB90275F594692B22C786B193FE71D86094" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9D4002D-BA40-4BE3-8930-F00A7B184761}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Børnejournalsystemer">'Opdateret d. 09-10-2026'!$A$1:$F$62</definedName>
+    <definedName name="Børnejournalsystemer">'Opdateret d. 23-10-2026'!$A$1:$F$62</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
